--- a/excel/chapters/main3.xlsx
+++ b/excel/chapters/main3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\p2n\scripts\chapters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\p2n\excel\chapters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1F5117-C421-4D11-B4C4-7A5E0EA194B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F7BE31-CCFD-4D89-8C12-20848AA924A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29310" yWindow="570" windowWidth="18390" windowHeight="15255" activeTab="9" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
+    <workbookView xWindow="29310" yWindow="570" windowWidth="18390" windowHeight="15255" firstSheet="3" activeTab="13" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
   </bookViews>
   <sheets>
     <sheet name="3-1" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="833">
   <si>
     <t>speaker</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2384,6 +2384,717 @@
   <si>
     <t>미끼가 제대로 작용했군. 이제 다 모였어.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조야는 악담을 퍼붓고는 곧바로 컨테이너에서 뛰어내려 땅에 세게 부딪히며 착지했다. 그러고는 누군가의 멱살을 잡아당겼다.</t>
+  </si>
+  <si>
+    <t>파편들이 그의 얼굴 위로 떨어졌고, 이는 그를 울부짖게 했다.</t>
+  </si>
+  <si>
+    <t>그는 애절하게 울었지만, 조야의 표정은 점점 차가워질 뿐이었다. 그녀는 조용히 그의 긴 칼을 뽑아 들었는데, 칼등에 작은 붉은색 결정이 박혀있었다.</t>
+  </si>
+  <si>
+    <t>그녀는 맨손으로 변이 장도를 쪼갠 후, 야나기의 목을 졸랐다.</t>
+  </si>
+  <si>
+    <t>조야가 손에 힘을 주자 야나기의 책임자가 신음을 내뱉더니 더는 아무 소리를 내지 못했다.</t>
+  </si>
+  <si>
+    <t>사방이 쥐 죽은 듯이 적막해졌다. 한참 후, 조야가 군단을 향해 몸을 돌렸고, 목소리는 평정을 되찾았다.</t>
+  </si>
+  <si>
+    <t>조야는 당신을 쳐다보지 않고 지나쳤지만, 그녀의 눈에서 불꽃을 봤다.</t>
+  </si>
+  <si>
+    <t>또 그 차가운 불꽃이었다. 당신은 마침내 그녀의 눈에는 미래가 없고, 과거의 파멸과 죽음에만 집착하고 있다는 것을 깨달았다.</t>
+  </si>
+  <si>
+    <t>반드시 그녀에게서 벗어나야 했다.</t>
+  </si>
+  <si>
+    <t>다 두목의 명령이야, 나, 난 그저 돈 받고 일하는 직원일 뿐이라고, 나도 억지로 하는 거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야나기 책임자</t>
+  </si>
+  <si>
+    <t>으아아아악, 살려, 살려줘! 항복할게!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>난 살고 싶어, 살아남으려면 무조건 갱단에 빌붙어야 해, 당신도 알다시피 신디케이트가 원래 이렇잖아! 다른 방법이 없다고!</t>
+  </si>
+  <si>
+    <t>살려줘… 나도 억지로 하는 거야, 삶이 날 이렇게 만들었어, 이건 신디케이트 탓이야!!</t>
+  </si>
+  <si>
+    <t>…어?</t>
+  </si>
+  <si>
+    <t>으, 으억… 신디케이트가… 날… 이렇게 만든 거야… 나만 그런 게 아니라 다들 이렇다고…</t>
+  </si>
+  <si>
+    <t>날 놔줘, 당신은 이미 이겼어, 당신을 이길 자가 없다고. 규칙에 따라 당신이 신디케이트의 제왕이야, 당신이 대장이라고! 당신이 하라는 대로 다할게, 살려줘!</t>
+  </si>
+  <si>
+    <t>좋은 칼을 가졌군.</t>
+  </si>
+  <si>
+    <t>변이 무기군, 야나기 내부에서 표창으로 주는 고급품이야. 잘 관리한 걸 보니 이걸 아주 아끼고 자랑스럽게 생각하나 보군.</t>
+  </si>
+  <si>
+    <t>이걸로 얼마나 많은 사람을 베어야 그런 영광을 얻을 수 있지?</t>
+  </si>
+  <si>
+    <t>그중에 아이, 평민, 무고한 사람이 얼마나 많이 포함되어있지? 그들은 죽었어? 아니면 변이됐어?</t>
+  </si>
+  <si>
+    <t>칼을 휘두를 때, 기분이 좋아? 뿌듯해? 공로를 되뇌면서 표창 받을 걸 생각해?</t>
+  </si>
+  <si>
+    <t>이런 좋은 칼 얼마나 더 가지고 있어?</t>
+  </si>
+  <si>
+    <t>…맞아. 신디케이트 잘못이지. 내가 그걸 모조리 파괴해버릴 거야, 너까지 포함해서.</t>
+  </si>
+  <si>
+    <t>넌 진작에 그것의 일부가 됐어.</t>
+  </si>
+  <si>
+    <t>제왕? 후, 바로 그 탐욕 때문에 여기가 이 모양이 된 거야.</t>
+  </si>
+  <si>
+    <t>난 너희들의 왕이 되지 않을 거야, 난 너희들이 죽는 걸 바래.</t>
+  </si>
+  <si>
+    <t>손을 너무 빨리 썼군, 다른 놈들을 더 고문해서 유산이 어디 있는지 알아내. 누가 그들을 불러냈고, 누가 그들에게 무기를 줬는지도.</t>
+  </si>
+  <si>
+    <t>당신도 마찬가지였다, 정부 기관의 '졸개'인 당신은 그녀에게 적이었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞에 지하 깊은 곳으로 통하는 거대한 화물용 엘리베이터가 있었는데, 최근까지 자주 사용됐던 흔적이 있었다.</t>
+  </si>
+  <si>
+    <t>주변 컨테이너에는 각종 변이 무기가 싸여있었다.</t>
+  </si>
+  <si>
+    <t>바닥 아래의 솟구침이 점점 격렬해졌다. 수감자가 붕괴할 때의 느낌과 비슷했고, 심지어 그보다 더 구역질 나게 했다.</t>
+  </si>
+  <si>
+    <t>…이 여자가 하자는 대로 해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어? 반항 안 하네?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른 사람 없을 때 내가 당신을 해칠 거라고는 생각 안 해?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>확실히 당신은 그런 우둔한 계획을 하고 있지 않았다.</t>
+  </si>
+  <si>
+    <t>이렇게 서두르는 걸 보니, 당신 부하한테 무슨 일이 있는 걸 아나 본데?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 사람의 안색이 동시에 어두워졌다. 야나기가 말한 것이 사실인 듯 했다. 하지만 지금 그건 중요하지 않았다.</t>
+  </si>
+  <si>
+    <t>조야&amp;켈시</t>
+  </si>
+  <si>
+    <t>▶ 당신한테 반항하는 건 의미가 없으니까</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후훗, 야나기랑 대적할 때는 지금보다 더 기개가 있던데.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조야는 당신을 높이 평가하는 듯한 말투로 이야기했다. 하지만 그런 것을 신경 쓸 바가 아니었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 없으면, 너도 살아서 나올 수 없어.</t>
+  </si>
+  <si>
+    <t>내가 없으면, 너도 살아서 나올 수 없어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게다가, 날 죽이고 싶어 하는 자들이 그렇게도 많았는데, 넌 그들 같은 눈빛을 가지고 있지 않아.</t>
+  </si>
+  <si>
+    <t>당신은 조야와 함께 내려갈 생각이 전혀 없었다.</t>
+  </si>
+  <si>
+    <t>오염 유탄 몇 발이 옆에 쌓여있던 무기 상자를 폭파하자 새까만 가시가 돋치더니 한곳에 모여 불결한 파충류들이 되었다.</t>
+  </si>
+  <si>
+    <t>아니다. 이번 시나리오는 당신이 정할 것이다.</t>
+  </si>
+  <si>
+    <t>됐어, 우리가 알아서 싸울 수 있어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야나기 잔당이 포효하며 헤카테를 향해 돌진했다, 그는 히스테리가 발작한 듯 공포에 휩싸인 채 움직였다. 바로 지금이었다…</t>
+  </si>
+  <si>
+    <t>당신은 헤카테를 밀치고 그녀를 대신해 폭도의 손아귀에 넘어갔다.</t>
+  </si>
+  <si>
+    <t>당신이 입모양으로 말하자, 헤카테는 당신이 하고 싶은 말을 이해한 듯 악몽을 시전하려던 손을 멈췄다. 순간 늘 변함 없던 얼굴에 곤혹스러움이 비쳤다.</t>
+  </si>
+  <si>
+    <t>곧바로 잔당의 칼이 당신의 목을 겨눴다.</t>
+  </si>
+  <si>
+    <t>켈시: 어떻게 된 거지?</t>
+  </si>
+  <si>
+    <t>잔당은 당신을 끌어당기며 한 발짝씩 등 뒤의 비밀 통로로 물러났다.</t>
+  </si>
+  <si>
+    <t>예상치 못한 일에 군단 전체가 멈추어 섰다. 켈시는 망설이며 당신을 봤다가 자기 단장을 보고는 별다른 행동을 하지 않았다.</t>
+  </si>
+  <si>
+    <t>하지만 조야는 당신의 눈을 똑바로 바라보기만 하고 웃었다.</t>
+  </si>
+  <si>
+    <t>조야의 눈빛이 당신을 뚫을 듯하자, 예의상 살짝 몸부림을 쳤다.</t>
+  </si>
+  <si>
+    <t>헤카테는 조용히 폭주하는 엘라를 진정시켰고, 조야는 그 자리에 서서 야나기가 당신을 거칠게 끌고 좁은 골목으로 들어가는 걸 바라봤다. 조야가 마지막에 뭐라고 했는지는 알아들을 수가 없었다.</t>
+  </si>
+  <si>
+    <t>그는 오염된 무기 상자를 갈라서 연 후, 가시를 폭파해 길을 막고 당신을 난폭하게 어둠 속으로 밀어 넣었다.</t>
+  </si>
+  <si>
+    <t>…당신이 군단에서 벗어나는 첫걸음이었다.</t>
+  </si>
+  <si>
+    <t>야나기 잔당</t>
+  </si>
+  <si>
+    <t>수리 잔당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내려갈 생각은 하지 마라! 당신이 유산을 손에 넣게 두지 않을 테니, 신디케이트 역시 당신에게 넘어가지 않을 것이다!! 당신들은 전부 여기에서 죽게 될 것이다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'하지 마'.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다가오지 마!! 다가오면 이 여자의 목을 잘라버리겠어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하, 하하… 이래도 당신이 저들의 적이라고 할 수 있겠나… 군단이 당신을 꽤 중요하게 생각하는군… 당신은 이제 인질이야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…후후, 우리…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>젠장, 조야! 거기 서서 뭐 해, 어서 구하라고, 너 때문에 붙잡혀 간 거잖아…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망할, 국장을 돌려줘!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기가 바로 무기고였군, 훗, 어쩐지 감히 나한테 와서 시비를 걸더라니.</t>
+  </si>
+  <si>
+    <t>좋아, 다들 남아서 경비를 서, 그러는 김에 여기에 있는 쓰레기들도 없애고.</t>
+  </si>
+  <si>
+    <t>이제 나랑 관리국 사람은 내려가서 유산을 회수할 거야.</t>
+  </si>
+  <si>
+    <t>넌 안 가도 돼, 내가 원하는 건 당신네 국장이 따라오는 거니까.</t>
+  </si>
+  <si>
+    <t>…그물을 빠져나간 물고기가 있었군. 켈시, 관리국 사람들을 잘 지켜.</t>
+  </si>
+  <si>
+    <t>…후훗, 그래. 못 버티겠으면 언제든 살려달라고 소리쳐.</t>
+  </si>
+  <si>
+    <t>이번엔 내가 널 구해주지.</t>
+  </si>
+  <si>
+    <t>………………</t>
+  </si>
+  <si>
+    <t>살려달라고 소리 안 치네?</t>
+  </si>
+  <si>
+    <t>그게 무슨 헛소리야, 온종일 싸웠다고, 누가 같이 내려가서 목숨 내놓겠대?</t>
+  </si>
+  <si>
+    <t>너!</t>
+  </si>
+  <si>
+    <t>소용없어, 목숨을 갖다 바치는 격이야. 이제 어떻게 할지 생각하자고, 조야랑 같이 내려갈 수는 없어…</t>
+  </si>
+  <si>
+    <t>헤카테, 오른쪽에서 습격해오려고 해!</t>
+  </si>
+  <si>
+    <t>야나기가 말한 게 진짜였어, 정말 매복이 있어.</t>
+  </si>
+  <si>
+    <t>봤어.</t>
+  </si>
+  <si>
+    <t>…!! 국장님!</t>
+  </si>
+  <si>
+    <t>여기가 바로 중앙 엘리베이터야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상은 창고일 뿐이고, 무기 조립 설비는 유산과 함께 지하에 있을 거야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 한 비밀 창고로 끌려갔다. 괴이한 무기 상자가 거칠게 뜯어진 채, 바닥에 난잡하게 쌓여있었다. 열 몇 쯤 되는 남아있는 사람들은 모여서 도망칠 궁리를 하고 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 바닥에 누워 정보를 들으려 안간힘을 쓰며, 고통을 참으면서 몸속의 족쇄를 느꼈다, 족쇄 다른 쪽 끝에 있는 수감자들의 존재를 느꼈다.</t>
+  </si>
+  <si>
+    <t>유독 힘이 강한 사람은 이미 내려갔고, 다른 두 사람은 당신 쪽으로 다가오고 있다. 아마 누군가가 운 좋게 당신이 남긴 흔적을 추적한 듯했다.</t>
+  </si>
+  <si>
+    <t>당신의 도박은 반은 성공적이었다. 야나기가 말한 것처럼 지하의 상황은 이미 조야의 통제를 넘어섰다. 조야는 당신에게 시간을 낭비하지 않고, 내려가는 것을 선택할 것이 틀림없었다.</t>
+  </si>
+  <si>
+    <t>하지만 그녀가 돌아오기 전에 켈시가 엘리베이터 입구를 가로막을 것이 분명했다. 그는 자기 단장을 내버려 두지 못할 것이었고, 단장이 오염될 수 있으니 당신을 죽이지도 못할 것이었다.</t>
+  </si>
+  <si>
+    <t>두 수감자가 당신을 찾아내게만 하면 됐다. 이런 생각을 하던 중, 당신을 납치한 자가 앞에 나타났다.</t>
+  </si>
+  <si>
+    <t>그는 당신을 거칠게 잡아당겼다. 말다툼, 그리고 패배했다는 사실이 그를 짜증나게 한 것이었다.</t>
+  </si>
+  <si>
+    <t>당신을 시간을 끌어야 했다, 적어도 헤카테와 엘라가 당신을 찾기 전까지 이동해서는 안 됐다. 이런 생각을 하며 이를 악물고 냉랭한 미소를 지었다.</t>
+  </si>
+  <si>
+    <t>주먹이 당신의 머리를 세게 강타했다. 양복 차림의 이 남자는 점젆은 모습을 집어치우고 당신의 멱살을 움켜쥔 채 악을 썼다.</t>
+  </si>
+  <si>
+    <t>그는 두 눈이 벌겋게 충혈된 채 쉬지 않고 당신을 후려치며 히스테리를 부렸다. 무능한 패자의 분노 표출이었다.</t>
+  </si>
+  <si>
+    <t>극심한 통증에 감각은 잃었지만, 정신은 멀쩡했다. 그가 목소리를 조금 더 높인다면 수감자들이 들을 수 있지 않을까?</t>
+  </si>
+  <si>
+    <t>탕…!! 큰 소리가 나더니 당신 뒤쪽에서 검은 실루엣이 튀어나와, 당신을 구타한 남자를 향해 돌진했다. 남자는 총탄에 맞아 비명을 지르며 몇 미터 떨어진 선반에 부딪혔다.</t>
+  </si>
+  <si>
+    <t>끓어오르는 듯한 형체의 악몽이 당신 앞을 가로막았다. 악몽에서 이따금 묵직한 굉음이 들려왔는데, 마치 불길 같은 분노로부터 무언가가 타오르는 듯했다.</t>
+  </si>
+  <si>
+    <t>동시에 등 뒤에서 소녀의 목소리가 들려왔다.</t>
+  </si>
+  <si>
+    <t>자제해야 하지 않겠어? 당신, 인질로 목숨을 부지하는 거잖아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흠… 졌다고 한심하게 화풀이나 하고 있다니, 부끄럽지도 않나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>온기가 있는 두 손이 살며시 당신 등을 잡아, 상처투성이인 당신의 몸을 지탱했다. 당신은 드디어 안심할 수 있었다.</t>
+  </si>
+  <si>
+    <t>그렇게 아프지는 않다고 하려 했지만, 이 둘이 당신을 이렇게나 걱정하는 건 드문 일이었으니…</t>
+  </si>
+  <si>
+    <t>그냥 이렇게 있기로 했다.</t>
+  </si>
+  <si>
+    <t>중앙 엘리베이터에서 이곳까지 오는 것은 결코 쉬운 일이 아니었다.</t>
+  </si>
+  <si>
+    <t>헤카테의 목소리는 여전히 담담했고 높낮이가 없었다. 그때 악몽이 곁으로 날아와 당신을 가볍게 문질렀다.</t>
+  </si>
+  <si>
+    <t>날 어떻게 찾은 거지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기도 그래, '그들'이 준 무기야, 더 많고, 더 강한 변이 무기!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야나기 잔당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자네는 이런 일을 떨쳐내지 못할 거야! 지난번에 도망친 자는 돌아가서 자기네 두목한테 죽지 않았나. 이건 '&lt;org&gt;그들&lt;/org&gt;'의 일이야, 자네가 할 수밖에 없어! 우린 반드시 군단을 없애야 하네!</t>
+  </si>
+  <si>
+    <t>그렇다면, 인질이 있어. 조야는 그 사람을 필요로 해, 최소한…</t>
+  </si>
+  <si>
+    <t>…그래.</t>
+  </si>
+  <si>
+    <t>이 길 밖에 없고, 밑에 유산이 있어, 운이 좋으면 전세를 역전할 수도 있어. 인질을 데려가자고.</t>
+  </si>
+  <si>
+    <t>일어나! 가자고!</t>
+  </si>
+  <si>
+    <t>쓸모만 없었다면, 내가 진작에 네놈을 죽였어.</t>
+  </si>
+  <si>
+    <t>이 미친 ** 군단의 졸개 주제에! 그 입 다물어! 다물라고!!</t>
+  </si>
+  <si>
+    <t>그때 네가 우리한테 사기치지만 않았다면 야나기 부대는 여기서 좌절하지 않았을 거야, 군단에게 패하지 않았을 거라고!</t>
+  </si>
+  <si>
+    <t>네놈이 이렇게 만들었어!!</t>
+  </si>
+  <si>
+    <t>너 이 **!!! 쏴 죽여주마!!</t>
+  </si>
+  <si>
+    <t>가자… 아래로 향하는 두 번째 굴, 유산으로부터 더 가까운 길이… 바로 여기에 있어…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만령회 잔당</t>
+  </si>
+  <si>
+    <t>당신들도 봤잖아, 그 여자가 어떻게 된 건지 이번에는 오염을 전혀 안 무서워해! 우린 절대 못 이길 거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리 잔당</t>
+  </si>
+  <si>
+    <t>난 안 해, 돌아갈 거야! 믿지 말아야 했어, 당신네 그 악…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기가 무슨 소용이야! 몇백 명이 왔는데 지금 우리 열 몇 명밖에 안 남았잖아. 변이 무기를 얼마나 더 가지든 무슨 소용이 있겠어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유산… 우리에겐 아직 유산이 있지… 거기에 만령의 의지가 있다. 그 여자가 걷는 길에는 함정이 가득해, 만령회가 그들에게 천벌을 내릴 것이야…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제가 보지 못하는 곳에서 다치지 마십시오, 국장님.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너… 너무 빨라… 찾았어? 찾았어?! 아, ○○, 너…</t>
+  </si>
+  <si>
+    <t>** 제길! 이 ****!! 어떤 놈이 이래 놓은 거야! 나와!!</t>
+  </si>
+  <si>
+    <t>후… 후… 좀 어때, 아직도 많이 아파?</t>
+  </si>
+  <si>
+    <t>힝, 우리 ○○ 어쩌다 이렇게 두들겨 맞은 거야, 나도 이렇게 때려본 적 없는데… 멀쩡히 있다가 왜 화를 돋운거야?</t>
+  </si>
+  <si>
+    <t>국장님께서 전에 이렇게 명령하셨었지요, 곁에서 마지막까지 국장님을 지키라고요. 그러니 더는 제 시야에서 벗어나지 마십시오.</t>
+  </si>
+  <si>
+    <t>국장님이 족쇄로 수감자를 찾아낼 수 있는 것처럼, 저희도 국장님의 존재를 감지할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>아주 미약했지만, 국장님의 고함을 들을 수 있었습니다, 족쇄의 다른 쪽 끝에서 말입니다.</t>
+  </si>
+  <si>
+    <t>그게 있었기에 국장님 곁으로 돌아갈 수 있었습니다.</t>
+  </si>
+  <si>
+    <t>그럼 이 둘을 풀어 주고 당신을 구하게 한 건, 당신의 족쇄를 지키는 동시에 갱단 잔당까지 없애려던 수였을까?</t>
+  </si>
+  <si>
+    <t>적어도 조야가 지상으로 돌아가기 전까지 당신은 안전하고 자유로울 것이었다. 게다가 당신은 목표물에 가장 가까이 접근해있었다.</t>
+  </si>
+  <si>
+    <t>&lt;org&gt;유산&lt;/org&gt;… 우리에겐 아직 유산이 있지… 거기에 만령의 의지가 있다. 그 여자가 걷는 길에는 함정이 가득해, 만령회가 그들에게 천벌을 내릴 것이야…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만령회</t>
+  </si>
+  <si>
+    <t>가자… &lt;org&gt;아래로 향하는 두 번째 굴&lt;/org&gt;, 유산으로부터 더 가까운 길이… 바로 &lt;org&gt;여기&lt;/org&gt;에 있어…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갱단들이 두고 간 무기 상자를 걷어차 여니, 안에 변이 무기가 가득했다.</t>
+  </si>
+  <si>
+    <t>테드의 말에 의하면 변이 결정은 희귀품인데, 이곳 갱단 사람들은 모두 하나씩 가지고 있었다. 무기도 그렇고, 유산에 대한 소문도 ‘그들’이 퍼뜨린 것이었다.</t>
+  </si>
+  <si>
+    <t>엘라는 갱단에 의해 억지로 열린 무기 상자에서 부서진 병을 꺼내 들었다. 안에는 핏빛 액체가 조금 남아있었다.</t>
+  </si>
+  <si>
+    <t>…아냐, 우린 계속 여길 조사할 거야</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'그들'은 도대체 누구일까? 유산, 이 변이 위기와 어떤 관계가 있는 걸까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Type99]: 정체불명의 붉은 액체가 가득 차 있는 샘플관. 외부에 ‘&lt;org&gt;PARMA-TYPE 99&lt;/org&gt;'라 적힌 태그가 붙어있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 구석에 원 모양이 인쇄되어있었고, 원 안에 &lt;org&gt;P&lt;/org&gt;자가 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>액체 상태의 변이 결정인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿵…… 쿵… 쿵……</t>
+  </si>
+  <si>
+    <t>강한 진동이 당신의 질문을 차단했다. 거대한 심장 박동 같은 것이 바닥에서부터 전해졌는데, 유산의 존재를 이렇게 강렬하게 느낀 것은 처음이었다.</t>
+  </si>
+  <si>
+    <t>악몽이 엘라가 들고 있던 병을 쳐 떨어뜨렸다. 바닥에 떨어지자, 갑자기 수많은 검은 가시가 돋치더니 꿈틀거리며, 마치 생명이 있기라도 한 듯 미친 듯이 증식했다.</t>
+  </si>
+  <si>
+    <t>누구?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무슨 실험?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닥이 갑자기 갈라지더니, 더 길고, 더 날카로운 수많은 가시 모양의 오염이 시멘트를 뚫고 나왔다. 당신들은 아래로 추락했고, 다른 층의 공간으로 떨어졌다.</t>
+  </si>
+  <si>
+    <t>이곳에는 P자가 새겨진 무기 상자가 더 많이 쌓여있었고, 그것들은 내부에서 터져, 오염이 넘쳐 나오고 있었다.</t>
+  </si>
+  <si>
+    <t>꿈틀대는 오염 속에서 불결한 괴물이 하나둘 생겨났다!</t>
+  </si>
+  <si>
+    <t>국장님이 생각하신 것처럼 조야가 혼자 중앙 엘리베이터를 타고 내려갔습니다. 켈시는 문을 지켰고요.</t>
+  </si>
+  <si>
+    <t>지하의 지세가 그들에게도 아주 불리했습니다, 그래서 군단은 국장님까지 막을 여력이 없었지요.</t>
+  </si>
+  <si>
+    <t>국장님이 군단의 통제에서 벗어나려면, 조야가 지상으로 돌아가기 전에 어떻게든 관리국에 연락을 취해 켈시의 능력을 해제할 방법을 찾아야 합니다.</t>
+  </si>
+  <si>
+    <t>가자, 엘라, 여길 떠나야 해.</t>
+  </si>
+  <si>
+    <t>하지만…</t>
+  </si>
+  <si>
+    <t>…! 엘라, 손 놔!</t>
+  </si>
+  <si>
+    <t>오염이야, 그 정도의 변이 결정이 이렇게 커진다니…</t>
+  </si>
+  <si>
+    <t>……!!</t>
+  </si>
+  <si>
+    <t>엘라! 집중해! 전투해야 해!!</t>
+  </si>
+  <si>
+    <t>잠깐… 나… 이게 뭔지 알아.</t>
+  </si>
+  <si>
+    <t>…………………</t>
+  </si>
+  <si>
+    <t>아니… 그렇게 불릴만한 게 아니야… 드디어 알았어, 진작 알아봤어야 했는데…</t>
+  </si>
+  <si>
+    <t>변이 결정은 바로 수감자의 몸에서 짜낸 물건이야, 이건 그놈들이 한 실험이야…</t>
+  </si>
+  <si>
+    <t>그런데 이게 왜 여기에 있지… 그 자식들 분명 진작에…</t>
+  </si>
+  <si>
+    <t>왜 여기 있는 거지, 그 자식들은 이미…</t>
+  </si>
+  <si>
+    <t>설마 그 여자를 찾으러 온 건가…?!</t>
+  </si>
+  <si>
+    <t>엘라는 붉은빛의 시작점을 향해 달려갔다, 부서진 비밀 문이었다.</t>
+  </si>
+  <si>
+    <t>엘라를 쫓아가!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비밀 문 안쪽은 협소하고 은밀한 실험실이었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>펑……!!!</t>
+  </si>
+  <si>
+    <t>또 한 차례의 박동이 일어나더니 병 몇 개가 동시에 터졌고, 붉은색의 액체가 바닥에 온통 튀었다.</t>
+  </si>
+  <si>
+    <t>빛이 붉은 액체로 가득 찬 병을 투과해 협소한 공간 전체를 붉은색으로 물들였다. 병에는 '&lt;org&gt;PARMA-Type 99&lt;/org&gt;'이라는 글자가 인쇄되어있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닥의 액체가 천천히 응고되더니 몇 개의 불길한 형태를 만들어냈다. 이목구비가 뚜렷하지는 않았지만, 뿜어져 나오는 광기와 살기는 누군가를 떠올리게 했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리를 습격한 군단의 용병인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘라는 왜곡된 에일리언을 멍하니 바라보며 온몸을 부들부들 떨었다.</t>
+  </si>
+  <si>
+    <t>하지만 그녀는 못 견디겠다는 듯 바닥에 엎어져 헛구역질하기 시작했다.</t>
+  </si>
+  <si>
+    <t>이름이 나인티나인이야?</t>
+  </si>
+  <si>
+    <t>무슨 일이 있었던 거야?</t>
+  </si>
+  <si>
+    <t>엘라는 땅에 주먹을 내리쳤다, 손이 베였고 박힌 파편이 그녀의 재생을 방해했다.</t>
+  </si>
+  <si>
+    <t>당신은 아무 말 없이 엘라의 손을 잡고 위로했다.</t>
+  </si>
+  <si>
+    <t>'유산'의 영향인 것이 틀림없어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 두 번째 엘리베이터를 찾았다. 반쯤 열린 문 사이로 끊임없이 오염이 넘쳐 나왔다.</t>
+  </si>
+  <si>
+    <t>이곳과 지하의 어떤 존재가 연결되어있어 그 영향을 받는 것이 틀림없었다, 심지어… 그 유산도 이미 제어가 불가능한 상태일 수도 있었다.</t>
+  </si>
+  <si>
+    <t>전례 없는 악의 힘인 것이 분명했다, 더욱 두렵고 더욱 거대한 존재일 것이었다. 당신은 공포를 느꼈다, 도망치고 싶어서가 아니었다…</t>
+  </si>
+  <si>
+    <t>일종의 예감에 대한 공포였다. 그대로 내버려 두면 더 무서운 재난을 가져올게 분명했다.</t>
+  </si>
+  <si>
+    <t>하지만 지하의 유산이 더 위험했다, 그것을 가지려고 다가가는 자는 더 위험했다.</t>
+  </si>
+  <si>
+    <t>떠날 것인가, 아니면 계속해서 들어가야 할 것인가?</t>
+  </si>
+  <si>
+    <t>머릿속에 헤어지기 전 마지막 순간이 떠올랐다. 그 여자의 눈빛과 똑똑히 알아듣지 못했던 말이 이제 뚜렷하게 떠올랐다.</t>
+  </si>
+  <si>
+    <t>밑에서 봐.</t>
+  </si>
+  <si>
+    <t>그 여자의 입 모양은 이랬다.</t>
+  </si>
+  <si>
+    <t>국장님, 여긴 너무 위험합니다…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…변이 결정들이 폭주하고 있어요. 국장님, 서둘러 여길 떠나야 합니다. 바닥 아래에 아주 위험한 뭔가가 있습니다.</t>
+  </si>
+  <si>
+    <t>엘라…? 어디 가는 거야?</t>
+  </si>
+  <si>
+    <t>아니에요, 저건 오염의 중합체일 뿐이에요, 그 수감자보다 더 위험하지요. 이것도 변이 결정의 영향일까요?</t>
+  </si>
+  <si>
+    <t>엘라, 싸워야 해!</t>
+  </si>
+  <si>
+    <t>…엘라?! 뭐 하는 거야?</t>
+  </si>
+  <si>
+    <t>정신 차려, 저건 인간이 아니야.</t>
+  </si>
+  <si>
+    <t>그래도 이게 어떻게 된 일인지는 얘기해줘야지.</t>
+  </si>
+  <si>
+    <t>우린 지금껏 변이 결정이 이런 식으로 폭주하는 걸 본 적이 없었어요. 왜 수감자에서 채취된 게 오염으로 변하는 거죠?</t>
+  </si>
+  <si>
+    <t>…………바로 앞에 있어…</t>
+  </si>
+  <si>
+    <t>…………그 사악한 놈들! 바로 앞에 있어!</t>
+  </si>
+  <si>
+    <t>…………나인티나인…?</t>
+  </si>
+  <si>
+    <t>알거든!</t>
+  </si>
+  <si>
+    <t>이제 알겠어… 그래서 그 갱단들이 수감자의 힘을 쓸 수 있었던 거였어…</t>
+  </si>
+  <si>
+    <t>역겨워… 파르마의 망할 것들… 감히 이런 짓을 하다니… 이렇게…</t>
+  </si>
+  <si>
+    <t>…얘기하고 싶지 않아.</t>
+  </si>
+  <si>
+    <t>…이건 다 그 자식들이 벌인 실험이야.</t>
+  </si>
+  <si>
+    <t>병에 들어있는, 신디케이트 갱단이 빼앗은 변이 결정들은 전부 수감자 몸에서 짜낸 것이야.</t>
+  </si>
+  <si>
+    <t>변이 무기의 갖가지 변이 이능력은 전부 상응하는 능력을 갖춘 수감자의 몸에서 짜낸 거라고.</t>
+  </si>
+  <si>
+    <t>그 끔찍한 놈들이 우리를 괴롭힌 건, 바로 이런 것 때문이야.</t>
   </si>
 </sst>
 </file>
@@ -3429,7 +4140,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1375A01-563E-46F2-A02B-9F945F13A2CE}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -3749,6 +4460,200 @@
         <v>608</v>
       </c>
     </row>
+    <row r="41" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C41" s="4" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C42" s="4" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B44" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C47" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B54" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C55" s="4" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B56" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B57" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B58" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B59" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C60" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B61" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B62" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C63" s="4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B64" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="4" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C66" s="4" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C67" s="4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C68" s="4" t="s">
+        <v>621</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3758,7 +4663,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A25B896A-D7E8-44E1-98CF-9D93E08951E1}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -3800,6 +4705,450 @@
       <c r="B2" s="1"/>
       <c r="C2" s="5"/>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C4" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="4" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C8" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C30" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C36" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C42" s="4" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C43" s="4" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C45" s="7" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C46" s="4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="4" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="4" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C55" s="4" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C56" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B57" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C58" s="4" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B59" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C60" s="4" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C61" s="4" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C62" s="4" t="s">
+        <v>673</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3809,7 +5158,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC46C4A-C3C1-4913-B34F-B6B08CB4B988}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -3844,12 +5193,347 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="5"/>
+    <row r="2" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C2" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C13" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C14" s="4" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C15" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C16" s="4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C17" s="4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C20" s="4" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C21" s="4" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C23" s="4" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C27" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C28" s="4" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C31" s="4" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C32" s="4" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="4" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C37" s="4" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C44" s="4" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C45" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="4" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C52" s="4" t="s">
+        <v>721</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3860,7 +5544,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CBBE15-6014-43CB-A071-ECDFB5C4B231}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -3895,12 +5579,254 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="5"/>
+    <row r="2" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C4" s="4" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C8" s="4" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="4" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C13" s="4" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="7" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C16" s="4" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C18" s="4" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C26" s="4" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C27" s="4" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C29" s="4" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C32" s="4" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C33" s="4" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C37" s="4" t="s">
+        <v>771</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3911,7 +5837,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FEC9E4D-1BC2-47C1-B354-5864E5DC6C7E}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -3946,12 +5872,348 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="5"/>
+    <row r="2" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C6" s="4" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="4" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C10" s="4" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C13" s="4" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C14" s="4" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="4" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C19" s="4" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C25" s="4" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C36" s="4" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C37" s="4" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="7"/>
+    </row>
+    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C42" s="4" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C43" s="4" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C44" s="4" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C45" s="4" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C47" s="4" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C48" s="4" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C49" s="4" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="4" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="4" t="s">
+        <v>812</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6779,7 +9041,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>87</v>
       </c>
@@ -6787,7 +9049,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>87</v>
       </c>
